--- a/docs/sheet.xlsx
+++ b/docs/sheet.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>System Memory Map</t>
   </si>
@@ -123,10 +123,65 @@
     <t>UART Register Map</t>
   </si>
   <si>
-    <t>DOUT[15:0]</t>
-  </si>
-  <si>
-    <t>DIN[15:0]</t>
+    <t>BAUD</t>
+  </si>
+  <si>
+    <t>16'd0</t>
+  </si>
+  <si>
+    <t>Bit [15:0]: baudrate divisor (see table below)</t>
+  </si>
+  <si>
+    <t>Value = Fclk / 8 * B</t>
+  </si>
+  <si>
+    <t>DOUT</t>
+  </si>
+  <si>
+    <t>Buffer of TX</t>
+  </si>
+  <si>
+    <t>0x0008</t>
+  </si>
+  <si>
+    <t>DIN</t>
+  </si>
+  <si>
+    <t>Buffer of RX</t>
+  </si>
+  <si>
+    <t>0x000C</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>{1'b0, 1'b0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status of TX &amp; RX:
+2'bx1: TX is ready
+2'b1x: RX has received a byte</t>
+  </si>
+  <si>
+    <t>0x0010</t>
+  </si>
+  <si>
+    <t>CONTROL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit 1: Receive enable
+Bit 0: Transmit enable</t>
+  </si>
+  <si>
+    <t>Baudrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baudrate divisor value
+(F = 27 Mhz)</t>
+  </si>
+  <si>
+    <t>Error(%)</t>
   </si>
 </sst>
 </file>
@@ -172,12 +227,17 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE59A"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -207,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -244,6 +304,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -920,15 +983,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
-    <col min="2" max="2" width="19.285714285714285" customWidth="1"/>
-    <col min="3" max="3" width="13.571428571428571" customWidth="1"/>
-    <col min="4" max="4" width="21.857142857142858" customWidth="1"/>
-    <col min="5" max="5" width="32.57142857142857" customWidth="1"/>
-    <col min="6" max="26" width="13.571428571428571" customWidth="1"/>
+    <col min="2" max="2" width="27.142857142857142" customWidth="1"/>
+    <col min="3" max="3" width="15.428571428571429" customWidth="1"/>
+    <col min="4" max="4" width="24.428571428571427" customWidth="1"/>
+    <col min="5" max="5" width="50.42857142857143" customWidth="1"/>
+    <col min="6" max="6" width="36.42857142857143" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -957,7 +1021,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>26</v>
       </c>
@@ -968,10 +1032,13 @@
         <v>28</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>30</v>
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -979,16 +1046,192 @@
         <v>31</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="60.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" ht="40.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="9" ht="42.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="11"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>2400</v>
+      </c>
+      <c r="B10" s="13">
+        <v>1406</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.018</v>
+      </c>
+      <c r="D10" s="11">
+        <v>1406.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>4800</v>
+      </c>
+      <c r="B11" s="13">
+        <v>703</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.018</v>
+      </c>
+      <c r="D11" s="11">
+        <v>703.125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>9600</v>
+      </c>
+      <c r="B12" s="13">
+        <v>352</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.124</v>
+      </c>
+      <c r="D12" s="11">
+        <v>351.5625</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>19200</v>
+      </c>
+      <c r="B13" s="13">
+        <v>176</v>
+      </c>
+      <c r="C13" s="11">
+        <v>0.124</v>
+      </c>
+      <c r="D13" s="11">
+        <v>175.78125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="11">
+        <v>38400</v>
+      </c>
+      <c r="B14" s="13">
+        <v>88</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.124</v>
+      </c>
+      <c r="D14" s="11">
+        <v>87.8906025</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>57600</v>
+      </c>
+      <c r="B15" s="13">
+        <v>59</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0.693</v>
+      </c>
+      <c r="D15" s="11">
+        <v>58.59375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="11">
+        <v>115200</v>
+      </c>
+      <c r="B16" s="13">
+        <v>29</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1.024</v>
+      </c>
+      <c r="D16" s="11">
+        <v>29.296875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>230400</v>
+      </c>
+      <c r="B17" s="13">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11">
+        <v>4.632</v>
+      </c>
+      <c r="D17" s="11">
+        <v>14.6484375</v>
       </c>
     </row>
   </sheetData>
